--- a/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
@@ -438,6 +438,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -459,6 +460,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -487,6 +489,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -494,6 +497,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -501,6 +505,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -533,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,23 +769,6 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methanisation</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GWh</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2021 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,7 +1646,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1714,37 +1702,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Weight export</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
+          <t>N recycling rate of human excretion in urban area</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Weight for the optimization model</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Weight energy</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
+          <t>N recycling rate of human excretion in rural area</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Weight for the optimization model</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1761,7 +1753,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1778,41 +1770,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1829,7 +1821,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1846,7 +1838,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1863,7 +1855,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1880,41 +1872,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1931,7 +1923,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1948,7 +1940,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,7 +1957,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1982,7 +1974,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1999,7 +1991,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2016,7 +2008,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2033,7 +2025,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2050,7 +2042,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2067,7 +2059,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2084,7 +2076,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2101,7 +2093,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2118,7 +2110,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,7 +2127,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2152,7 +2144,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2169,7 +2161,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2186,7 +2178,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2203,7 +2195,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2220,7 +2212,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2237,7 +2229,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2254,7 +2246,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2271,7 +2263,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2288,12 +2280,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2305,12 +2297,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2322,7 +2314,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2339,7 +2331,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2356,7 +2348,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2373,7 +2365,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,41 +2382,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2441,7 +2433,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2458,7 +2450,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2475,7 +2467,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2492,12 +2484,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>kg/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2509,12 +2501,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>kg/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2526,7 +2518,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Caprines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2543,7 +2535,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Poultry dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2552,40 +2544,6 @@
         </is>
       </c>
       <c r="E55" t="inlineStr">
-        <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Caprines dairy productivity</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Poultry dairy productivity</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
@@ -438,9 +438,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -462,9 +460,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -493,9 +489,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -503,9 +497,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -513,9 +505,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -548,31 +538,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
@@ -589,8 +579,6 @@
           <t>M inhabitant</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>INSEE data</t>
@@ -608,8 +596,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Logistic</t>
@@ -627,8 +613,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -646,8 +630,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -665,8 +647,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -684,8 +664,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -703,8 +681,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -714,7 +690,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Net import of vegetal pdcts</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -722,66 +698,75 @@
           <t>ktN</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend. Used as a goal but may be adjusted according to territory situation</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>ktN</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>LU</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Synth N fertilizer application to cropland</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>kgN/ha/yr</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>kgN/ha/yr</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
         </is>
@@ -1159,7 +1144,6 @@
       <c r="E16" t="n">
         <v>30</v>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1179,7 +1163,6 @@
       <c r="E17" t="n">
         <v>35</v>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1507,7 +1490,6 @@
       <c r="E32" t="n">
         <v>14</v>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1585,6 @@
           <t xml:space="preserve">Natural meadow </t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="b">
         <v>0</v>
       </c>
@@ -1628,31 +1609,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -1664,11 +1645,9 @@
           <t>Weight diet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1681,11 +1660,9 @@
           <t>Weight synthetic fertilizer use</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1695,14 +1672,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Weight import/export balance</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Weight import</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1712,26 +1687,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1739,8 +1710,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1750,7 +1719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1758,8 +1727,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1769,7 +1736,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1777,8 +1744,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1788,26 +1753,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1815,8 +1778,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1826,7 +1787,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1834,8 +1795,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1845,7 +1804,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1853,8 +1812,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1864,7 +1821,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1872,8 +1829,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1883,7 +1838,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1891,8 +1846,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1902,26 +1855,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1929,8 +1880,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1940,7 +1889,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1948,8 +1897,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1959,7 +1906,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1967,8 +1914,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1978,7 +1923,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,8 +1931,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1997,7 +1940,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2005,8 +1948,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2016,7 +1957,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2024,8 +1965,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2035,7 +1974,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2043,8 +1982,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2054,7 +1991,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2062,8 +1999,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2073,7 +2008,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2081,8 +2016,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2092,7 +2025,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2100,8 +2033,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2111,7 +2042,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2119,8 +2050,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2130,7 +2059,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2138,8 +2067,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2149,7 +2076,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2157,8 +2084,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2168,7 +2093,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,8 +2101,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2187,7 +2110,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2195,8 +2118,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2206,7 +2127,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2214,8 +2135,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2225,7 +2144,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2233,8 +2152,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2244,7 +2161,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2252,8 +2169,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2263,7 +2178,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2271,8 +2186,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2282,7 +2195,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2290,8 +2203,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2301,7 +2212,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2309,8 +2220,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2320,7 +2229,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2328,8 +2237,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2339,7 +2246,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2347,8 +2254,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2358,16 +2263,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2377,7 +2280,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2385,8 +2288,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2396,7 +2297,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2404,8 +2305,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2415,7 +2314,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2423,8 +2322,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2434,7 +2331,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2442,8 +2339,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2453,7 +2348,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2461,8 +2356,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2472,26 +2365,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2499,8 +2390,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2510,7 +2399,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2518,8 +2407,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2529,7 +2416,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2537,8 +2424,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2548,7 +2433,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2556,8 +2441,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2567,7 +2450,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2575,8 +2458,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2586,16 +2467,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2605,7 +2484,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2613,8 +2492,6 @@
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2624,7 +2501,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2632,8 +2509,6 @@
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2643,17 +2518,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
@@ -438,7 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -460,7 +459,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -489,7 +487,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -497,7 +494,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -505,7 +501,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -538,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +764,23 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methanisation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2021 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,7 +1658,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1702,41 +1714,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1753,7 +1761,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1770,41 +1778,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1821,7 +1829,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1838,7 +1846,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1855,7 +1863,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1872,41 +1880,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,7 +1931,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1940,7 +1948,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1957,7 +1965,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1974,7 +1982,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1991,7 +1999,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2008,7 +2016,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2025,7 +2033,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2042,7 +2050,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2059,7 +2067,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2076,7 +2084,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2093,7 +2101,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2110,7 +2118,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2127,7 +2135,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2144,7 +2152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2161,7 +2169,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2178,7 +2186,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2195,7 +2203,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2212,7 +2220,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2229,7 +2237,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2246,7 +2254,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2263,7 +2271,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2280,12 +2288,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2297,12 +2305,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2314,7 +2322,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2331,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2348,7 +2356,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2365,7 +2373,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2382,41 +2390,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2433,7 +2441,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2450,7 +2458,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,7 +2475,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2484,12 +2492,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2501,12 +2509,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2518,7 +2526,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2535,15 +2543,49 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Ovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
@@ -438,7 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -460,7 +459,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -489,7 +487,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -497,7 +494,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -505,7 +501,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -538,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +764,23 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methaniser production</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh/yr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,7 +1658,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1702,24 +1714,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1736,7 +1746,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1753,7 +1763,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1770,24 +1780,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1804,7 +1814,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1821,7 +1831,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1838,7 +1848,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1855,7 +1865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1872,24 +1882,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1906,7 +1916,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,7 +1933,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1940,7 +1950,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1957,7 +1967,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1974,7 +1984,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1991,7 +2001,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2008,7 +2018,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2025,7 +2035,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2042,7 +2052,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2059,7 +2069,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2076,7 +2086,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2093,7 +2103,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2110,7 +2120,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2127,7 +2137,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2144,7 +2154,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2161,7 +2171,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2178,7 +2188,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2195,7 +2205,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2212,7 +2222,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2229,7 +2239,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2246,7 +2256,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2263,7 +2273,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2280,12 +2290,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2297,7 +2307,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2314,7 +2324,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2331,7 +2341,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2348,7 +2358,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2365,7 +2375,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2382,24 +2392,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2416,7 +2426,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2433,7 +2443,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2450,7 +2460,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,7 +2477,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2484,12 +2494,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2501,7 +2511,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2518,7 +2528,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2535,15 +2545,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
@@ -1621,7 +1621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1729,24 +1729,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight methaniser input</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1763,7 +1761,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1780,7 +1778,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1797,24 +1795,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1831,7 +1829,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1848,7 +1846,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1865,7 +1863,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1882,7 +1880,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1899,24 +1897,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,7 +1931,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1950,7 +1948,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1967,7 +1965,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1984,7 +1982,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2001,7 +1999,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2018,7 +2016,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2035,7 +2033,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2052,7 +2050,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2069,7 +2067,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2086,7 +2084,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2103,7 +2101,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2120,7 +2118,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2137,7 +2135,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2154,7 +2152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2171,7 +2169,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2188,7 +2186,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2205,7 +2203,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2222,7 +2220,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2239,7 +2237,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2256,7 +2254,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2273,7 +2271,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2290,7 +2288,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2307,12 +2305,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2324,7 +2322,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2341,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2358,7 +2356,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2375,7 +2373,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2392,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2409,24 +2407,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2443,7 +2441,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2460,7 +2458,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2477,7 +2475,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2494,7 +2492,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2511,12 +2509,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2528,7 +2526,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2545,7 +2543,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2562,17 +2560,134 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Share of crop residues in methaniser</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Share of green waste in methaniser</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Share of dedicated culture in methaniser</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Share of livestock effluent in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
         </is>
       </c>
     </row>

--- a/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
@@ -438,9 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -462,9 +459,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -493,9 +487,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -503,18 +494,12 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>BAU compute Business as usual scenario</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -548,31 +533,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
@@ -589,8 +574,6 @@
           <t>M inhabitant</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>INSEE data</t>
@@ -608,8 +591,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Logistic</t>
@@ -627,8 +608,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -646,8 +625,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -665,8 +642,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -684,8 +659,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -703,8 +676,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -714,7 +685,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Net import of vegetal pdcts</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -722,68 +693,94 @@
           <t>ktN</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend. Used as a goal but may be adjusted according to territory situation</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>ktN</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>LU</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Synth N fertilizer application to cropland</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>kgN/ha/yr</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>kgN/ha/yr</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methaniser production</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh/yr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1156,6 @@
       <c r="E16" t="n">
         <v>30</v>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1179,7 +1175,6 @@
       <c r="E17" t="n">
         <v>35</v>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1507,7 +1502,6 @@
       <c r="E32" t="n">
         <v>14</v>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1597,6 @@
           <t xml:space="preserve">Natural meadow </t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="b">
         <v>0</v>
       </c>
@@ -1628,31 +1621,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -1664,11 +1657,9 @@
           <t>Weight diet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>10</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1681,11 +1672,9 @@
           <t>Weight synthetic fertilizer use</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1695,14 +1684,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Weight import/export balance</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Weight import</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1712,64 +1699,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>Weight methaniser input</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1777,8 +1752,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1788,64 +1761,58 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1853,8 +1820,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1864,7 +1829,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1872,8 +1837,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1883,7 +1846,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1891,8 +1854,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1902,64 +1863,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1967,8 +1922,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1978,7 +1931,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,8 +1939,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1997,7 +1948,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2005,8 +1956,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2016,7 +1965,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2024,8 +1973,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2035,7 +1982,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2043,8 +1990,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2054,7 +1999,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2062,8 +2007,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2073,7 +2016,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2081,8 +2024,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2092,7 +2033,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2100,8 +2041,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2111,7 +2050,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2119,8 +2058,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2130,7 +2067,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2138,8 +2075,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2149,7 +2084,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2157,8 +2092,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2168,7 +2101,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,8 +2109,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2187,7 +2118,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2195,8 +2126,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2206,7 +2135,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2214,8 +2143,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2225,7 +2152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2233,8 +2160,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2244,7 +2169,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2252,8 +2177,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2263,7 +2186,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2271,8 +2194,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2282,7 +2203,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2290,8 +2211,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2301,7 +2220,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2309,8 +2228,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2320,7 +2237,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2328,8 +2245,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2339,7 +2254,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2347,8 +2262,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2358,16 +2271,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2377,16 +2288,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2396,16 +2305,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2415,7 +2322,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2423,8 +2330,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2434,7 +2339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2442,8 +2347,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2453,7 +2356,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2461,8 +2364,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2472,64 +2373,58 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2537,8 +2432,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2548,7 +2441,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2556,8 +2449,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2567,7 +2458,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2575,8 +2466,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2586,16 +2475,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2605,16 +2492,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2624,16 +2509,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2643,19 +2526,168 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Bovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Share of crop residues in methaniser</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Share of green waste in methaniser</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Share of dedicated culture in methaniser</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Share of livestock effluent in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
         </is>
       </c>
     </row>

--- a/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,24 +583,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Urban population</t>
+          <t>Total per capita protein ingestion</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN/cap/yr</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Logistic</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Total per capita protein ingestion</t>
+          <t>Vegetal per capita protein ingestion</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vegetal per capita protein ingestion</t>
+          <t>Edible animal per capita protein ingestion (excl fish)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -634,24 +634,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Edible animal per capita protein ingestion (excl fish)</t>
+          <t>Arable area</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kgN/cap/yr</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arable area</t>
+          <t>Permanent grassland area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -668,24 +668,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Permanent grassland area</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>ktN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Import of vegetal pdcts</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -702,41 +702,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Export of vegetal pdcts</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ktN</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Synth N fertilizer application to cropland</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>kgN/ha/yr</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -753,32 +753,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to grassland</t>
+          <t>Methaniser production</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
+          <t>GWh/yr</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methaniser production</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GWh/yr</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
@@ -1621,7 +1604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1650,6 +1633,11 @@
           <t>Comment</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1665,6 +1653,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1680,6 +1671,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1695,6 +1689,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1710,6 +1707,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1725,6 +1725,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1740,28 +1743,31 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+          <t>Urban population</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Logistic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1773,12 +1779,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1790,12 +1799,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1807,29 +1819,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Historical trend</t>
-        </is>
+          <t>Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1841,12 +1859,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1858,12 +1879,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1875,12 +1899,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1892,12 +1919,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1909,29 +1939,35 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
-        </is>
+          <t>Historical trend</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1943,12 +1979,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1960,12 +1999,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1977,12 +2019,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1994,12 +2039,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2011,12 +2059,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2028,12 +2079,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2045,12 +2099,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2062,12 +2119,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2079,12 +2139,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2096,12 +2159,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2113,12 +2179,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2130,12 +2199,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2147,12 +2219,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2164,12 +2239,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2181,12 +2259,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2198,12 +2279,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2215,12 +2299,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2232,12 +2319,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F36" t="n">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2249,12 +2339,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F37" t="n">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2266,12 +2359,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F38" t="n">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2283,12 +2379,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F39" t="n">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2300,12 +2399,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F40" t="n">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2317,29 +2419,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F41" t="n">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F42" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2351,12 +2459,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F43" t="n">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2368,12 +2479,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F44" t="n">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2385,12 +2499,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F45" t="n">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2402,12 +2519,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F46" t="n">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2419,29 +2539,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F47" t="n">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
+          <t>Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2453,12 +2579,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F49" t="n">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2470,12 +2599,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F50" t="n">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2487,12 +2619,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F51" t="n">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2504,12 +2639,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F52" t="n">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2521,29 +2659,35 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F53" t="n">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F54" t="n">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2555,12 +2699,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F55" t="n">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2572,12 +2719,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F56" t="n">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Poultry dairy productivity</t>
+          <t>Caprines dairy productivity</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2589,32 +2739,35 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F57" t="n">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Share of crop residues in methaniser</t>
+          <t>Poultry dairy productivity</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.06</v>
+          <t>kg/LU</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Adapted from ONRB data</t>
-        </is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Share of green waste in methaniser</t>
+          <t>Share of crop residues in methaniser</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2623,18 +2776,21 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F59" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Share of dedicated culture in methaniser</t>
+          <t>Share of green waste in methaniser</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2643,18 +2799,21 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F60" t="n">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Share of animal food industry in methaniser</t>
+          <t>Share of dedicated culture in methaniser</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2663,32 +2822,61 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F61" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Share of livestock effluent in methaniser</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>prop</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C63" t="n">
         <v>0.79</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F63" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Côte d'Azur.xlsx
@@ -778,38 +778,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Crops</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Area proportion (%)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Enforce Area</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ymax (kgN/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>k (kgN/ha)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>r2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Straw to Grain Ratio</t>
         </is>
       </c>
     </row>
@@ -834,6 +839,9 @@
       <c r="F2" t="n">
         <v>0.32</v>
       </c>
+      <c r="G2" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -856,6 +864,9 @@
       <c r="F3" t="n">
         <v>0.14</v>
       </c>
+      <c r="G3" t="n">
+        <v>0.042</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -878,6 +889,9 @@
       <c r="F4" t="n">
         <v>0.24</v>
       </c>
+      <c r="G4" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -900,11 +914,14 @@
       <c r="F5" t="n">
         <v>0.23</v>
       </c>
+      <c r="G5" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Grain maize</t>
+          <t>Maize</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -922,6 +939,9 @@
       <c r="F6" t="n">
         <v>0.65</v>
       </c>
+      <c r="G6" t="n">
+        <v>0.039</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -944,6 +964,9 @@
       <c r="F7" t="n">
         <v>0.96</v>
       </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -966,165 +989,186 @@
       <c r="F8" t="n">
         <v>0.63</v>
       </c>
+      <c r="G8" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Straw</t>
+          <t>Rapeseed</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1.203933864183619</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>419</v>
       </c>
       <c r="E9" t="n">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
+      </c>
+      <c r="G9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rapeseed</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.203933864183619</v>
+        <v>4.541294625797444</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>419</v>
+        <v>91</v>
       </c>
       <c r="E10" t="n">
-        <v>439</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
-        <v>0.68</v>
+        <v>0.21</v>
+      </c>
+      <c r="G10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Soybean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.541294625797444</v>
+        <v>0.2363796937997787</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>359</v>
       </c>
       <c r="E11" t="n">
-        <v>111</v>
+        <v>449</v>
       </c>
       <c r="F11" t="n">
-        <v>0.21</v>
+        <v>0.82</v>
+      </c>
+      <c r="G11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Soybean</t>
+          <t>Other oil crops</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2363796937997787</v>
+        <v>0.01602574195252737</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>359</v>
+        <v>655</v>
       </c>
       <c r="E12" t="n">
-        <v>449</v>
+        <v>503</v>
       </c>
       <c r="F12" t="n">
-        <v>0.82</v>
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Other oil crops</t>
+          <t>Horse beans and faba beans</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01602574195252737</v>
+        <v>0.0741190565304391</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>655</v>
+        <v>188</v>
       </c>
       <c r="E13" t="n">
-        <v>503</v>
+        <v>271</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.85</v>
+      </c>
+      <c r="G13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Horse beans and faba beans</t>
+          <t>Peas</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0741190565304391</v>
+        <v>0.8032903153704345</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>188</v>
+        <v>359</v>
       </c>
       <c r="E14" t="n">
-        <v>271</v>
+        <v>600</v>
       </c>
       <c r="F14" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
+      </c>
+      <c r="G14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Peas</t>
+          <t>Other protein crops</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8032903153704345</v>
+        <v>0</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>359</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>600</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.78</v>
+        <v>30</v>
+      </c>
+      <c r="G15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Other protein crops</t>
+          <t>Sugar beet</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1134,57 +1178,69 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="G16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sugar beet</t>
+          <t>Potatoes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.5268462666893373</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>339</v>
       </c>
       <c r="E17" t="n">
-        <v>35</v>
+        <v>576</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Potatoes</t>
+          <t>Other roots</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5268462666893373</v>
+        <v>0</v>
       </c>
       <c r="C18" t="b">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>339</v>
+        <v>63</v>
       </c>
       <c r="E18" t="n">
-        <v>576</v>
+        <v>150</v>
       </c>
       <c r="F18" t="n">
-        <v>0.28</v>
+        <v>0.57</v>
+      </c>
+      <c r="G18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other roots</t>
+          <t>Green peas</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1194,19 +1250,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E19" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F19" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
+      </c>
+      <c r="G19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Green peas</t>
+          <t>Dry beans</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1216,19 +1275,22 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>168</v>
       </c>
       <c r="E20" t="n">
-        <v>155</v>
+        <v>294</v>
       </c>
       <c r="F20" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
+      </c>
+      <c r="G20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dry beans</t>
+          <t>Green beans</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1238,19 +1300,22 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="E21" t="n">
-        <v>294</v>
+        <v>202</v>
       </c>
       <c r="F21" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
+      </c>
+      <c r="G21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Green beans</t>
+          <t>Dry vegetables</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1260,19 +1325,22 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="E22" t="n">
-        <v>202</v>
+        <v>11</v>
       </c>
       <c r="F22" t="n">
-        <v>0.83</v>
+        <v>0.08</v>
+      </c>
+      <c r="G22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dry vegetables</t>
+          <t>Dry fruits</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1282,19 +1350,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08</v>
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dry fruits</t>
+          <t>Squash and melons</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1304,19 +1375,22 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>205</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.78</v>
+      </c>
+      <c r="G24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Squash and melons</t>
+          <t>Cabbage</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1326,19 +1400,22 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>205</v>
+        <v>160</v>
       </c>
       <c r="E25" t="n">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="F25" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
+      </c>
+      <c r="G25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cabbage</t>
+          <t>Leaves vegetables</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1348,19 +1425,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="E26" t="n">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="F26" t="n">
-        <v>0.64</v>
+        <v>0.04</v>
+      </c>
+      <c r="G26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Leaves vegetables</t>
+          <t>Fruits</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1370,63 +1450,72 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="E27" t="n">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04</v>
+        <v>0.58</v>
+      </c>
+      <c r="G27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fruits</t>
+          <t>Olives</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>10.18035257534301</v>
       </c>
       <c r="C28" t="b">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="E28" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="F28" t="n">
-        <v>0.58</v>
+        <v>0.06</v>
+      </c>
+      <c r="G28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Olives</t>
+          <t>Citrus</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10.18035257534301</v>
+        <v>0</v>
       </c>
       <c r="C29" t="b">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E29" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
+      </c>
+      <c r="G29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Citrus</t>
+          <t>Hemp</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1436,19 +1525,22 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>0.15</v>
+        <v>-1.12</v>
+      </c>
+      <c r="G30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hemp</t>
+          <t>Flax</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1458,139 +1550,135 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-1.12</v>
+        <v>14</v>
+      </c>
+      <c r="G31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Flax</t>
+          <t>Forage maize</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>2.273652139514821</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>139</v>
       </c>
       <c r="E32" t="n">
-        <v>14</v>
+        <v>125</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forage maize</t>
+          <t>Forage cabbages</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.273652139514821</v>
+        <v>0.3499333214407352</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>139</v>
+        <v>230</v>
       </c>
       <c r="E33" t="n">
-        <v>125</v>
+        <v>202</v>
       </c>
       <c r="F33" t="n">
-        <v>0.24</v>
+        <v>0.54</v>
+      </c>
+      <c r="G33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Forage cabbages</t>
+          <t>Alfalfa and clover</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.3499333214407352</v>
+        <v>8.509668976792035</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>230</v>
+        <v>392</v>
       </c>
       <c r="E34" t="n">
-        <v>202</v>
+        <v>542</v>
       </c>
       <c r="F34" t="n">
-        <v>0.54</v>
+        <v>0.91</v>
+      </c>
+      <c r="G34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alfalfa and clover</t>
+          <t>Non-legume temporary meadow</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8.509668976792035</v>
+        <v>4.236805528699424</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>392</v>
+        <v>610</v>
       </c>
       <c r="E35" t="n">
-        <v>542</v>
+        <v>698</v>
       </c>
       <c r="F35" t="n">
-        <v>0.91</v>
+        <v>0.59</v>
+      </c>
+      <c r="G35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Non-legume temporary meadow</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>4.236805528699424</v>
+          <t xml:space="preserve">Natural meadow </t>
+        </is>
       </c>
       <c r="C36" t="b">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>610</v>
+        <v>34</v>
       </c>
       <c r="E36" t="n">
-        <v>698</v>
+        <v>62</v>
       </c>
       <c r="F36" t="n">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Natural meadow </t>
-        </is>
-      </c>
-      <c r="C37" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>34</v>
-      </c>
-      <c r="E37" t="n">
-        <v>62</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.21</v>
+      </c>
+      <c r="G36" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1653,9 +1741,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1671,9 +1756,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1689,9 +1771,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1707,9 +1786,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1725,9 +1801,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1743,9 +1816,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1780,9 +1850,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1800,9 +1867,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1820,9 +1884,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1840,9 +1901,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1860,9 +1918,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1880,9 +1935,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1900,9 +1952,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1920,9 +1969,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1940,9 +1986,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1960,9 +2003,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1980,9 +2020,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2000,9 +2037,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2020,9 +2054,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2040,9 +2071,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2060,9 +2088,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2080,9 +2105,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2100,9 +2122,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2120,9 +2139,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2140,9 +2156,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2160,9 +2173,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2180,9 +2190,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2200,9 +2207,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2220,9 +2224,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2240,9 +2241,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2260,9 +2258,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2280,9 +2275,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2300,9 +2292,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2320,9 +2309,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2340,9 +2326,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2360,9 +2343,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2380,9 +2360,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2400,9 +2377,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2420,9 +2394,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2440,9 +2411,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2460,9 +2428,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2480,9 +2445,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2500,9 +2462,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2520,9 +2479,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2540,9 +2496,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2560,9 +2513,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2580,9 +2530,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2600,9 +2547,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2620,9 +2564,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2640,9 +2581,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2660,9 +2598,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2680,9 +2615,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2700,9 +2632,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2720,9 +2649,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2740,9 +2666,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2760,9 +2683,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2783,9 +2703,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2806,9 +2723,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2829,9 +2743,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2852,9 +2763,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2874,9 +2782,6 @@
         <is>
           <t>Adapted from ONRB data</t>
         </is>
-      </c>
-      <c r="F63" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
